--- a/basedatos_partidas/salida/descompuestos/CT-07-03-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-07-03-050.xlsx
@@ -565,10 +565,10 @@
         <v>0.4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.48</v>
+        <v>0.32</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="12">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="13">
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="H21" t="n">
         <v>0.04</v>
@@ -743,7 +743,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-07-03-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-07-03-050.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 07 Frisos y revestimientos de pared</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Enchapado cerámico y porcelanato</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
